--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.0303939569993</v>
+        <v>9.104939018012386</v>
       </c>
       <c r="D2" t="n">
-        <v>37.47514503426073</v>
+        <v>6.089711068067368</v>
       </c>
       <c r="E2" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F2" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.57818659485326</v>
+        <v>5.943955321663655</v>
       </c>
       <c r="D3" t="n">
-        <v>12.93141620716035</v>
+        <v>2.101355133663557</v>
       </c>
       <c r="E3" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F3" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.62158980657388</v>
+        <v>4.813508343568256</v>
       </c>
       <c r="D4" t="n">
-        <v>19.00041193074781</v>
+        <v>3.087566938746519</v>
       </c>
       <c r="E4" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F4" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.37653289313877</v>
+        <v>4.28618659513505</v>
       </c>
       <c r="D5" t="n">
-        <v>27.56306943926675</v>
+        <v>4.478998783880846</v>
       </c>
       <c r="E5" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F5" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.3764741338879</v>
+        <v>2.498677046756784</v>
       </c>
       <c r="D6" t="n">
-        <v>25.22556300512676</v>
+        <v>4.099153988333098</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F6" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.36111111111112</v>
+        <v>1.521180555555557</v>
       </c>
       <c r="D7" t="n">
-        <v>25.16196501609273</v>
+        <v>4.088819315115068</v>
       </c>
       <c r="E7" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F7" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.9047846709004</v>
+        <v>8.272027509021315</v>
       </c>
       <c r="D8" t="n">
-        <v>46.06781110045469</v>
+        <v>7.486019303823888</v>
       </c>
       <c r="E8" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F8" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>63.3899684302209</v>
+        <v>10.3008698699109</v>
       </c>
       <c r="D9" t="n">
-        <v>57.4157490733378</v>
+        <v>9.330059224417393</v>
       </c>
       <c r="E9" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F9" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.17162306228277</v>
+        <v>3.76538874762095</v>
       </c>
       <c r="D10" t="n">
-        <v>33.9012096891154</v>
+        <v>5.508946574481254</v>
       </c>
       <c r="E10" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F10" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.99874520869222</v>
+        <v>4.549796096412486</v>
       </c>
       <c r="D11" t="n">
-        <v>22.59089529268045</v>
+        <v>3.671020485060573</v>
       </c>
       <c r="E11" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F11" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.04796258529654</v>
+        <v>1.957793920110688</v>
       </c>
       <c r="D12" t="n">
-        <v>3.453832724867155</v>
+        <v>0.5612478177909127</v>
       </c>
       <c r="E12" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F12" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.05461983982072</v>
+        <v>6.346375723970868</v>
       </c>
       <c r="D13" t="n">
-        <v>31.00830677035406</v>
+        <v>5.038849850182535</v>
       </c>
       <c r="E13" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F13" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.26358118052474</v>
+        <v>5.405331941835271</v>
       </c>
       <c r="D14" t="n">
-        <v>33.55562480244055</v>
+        <v>5.45278903039659</v>
       </c>
       <c r="E14" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F14" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.14893915299147</v>
+        <v>7.011702612361114</v>
       </c>
       <c r="D15" t="n">
-        <v>34.34002745011703</v>
+        <v>5.580254460644017</v>
       </c>
       <c r="E15" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F15" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.93532155379979</v>
+        <v>5.026989752492466</v>
       </c>
       <c r="D16" t="n">
-        <v>28.25112133415749</v>
+        <v>4.590807216800592</v>
       </c>
       <c r="E16" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F16" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.19226542774513</v>
+        <v>7.181243132008583</v>
       </c>
       <c r="D17" t="n">
-        <v>35.36200166996271</v>
+        <v>5.74632527136894</v>
       </c>
       <c r="E17" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F17" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>59.97326404093487</v>
+        <v>9.745655406651917</v>
       </c>
       <c r="D18" t="n">
-        <v>51.06604415806804</v>
+        <v>8.298232175686056</v>
       </c>
       <c r="E18" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F18" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>46.71267431645949</v>
+        <v>7.590809576424667</v>
       </c>
       <c r="D19" t="n">
-        <v>38.75300003514892</v>
+        <v>6.2973625057117</v>
       </c>
       <c r="E19" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F19" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>46.38402381223979</v>
+        <v>7.537403869488966</v>
       </c>
       <c r="D20" t="n">
-        <v>43.59512246084682</v>
+        <v>7.084207399887609</v>
       </c>
       <c r="E20" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F20" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>47.08709680037554</v>
+        <v>7.651653230061026</v>
       </c>
       <c r="D21" t="n">
-        <v>42.52376633320214</v>
+        <v>6.910112029145348</v>
       </c>
       <c r="E21" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F21" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>56.47550236767683</v>
+        <v>9.177269134747485</v>
       </c>
       <c r="D22" t="n">
-        <v>52.26262067738001</v>
+        <v>8.492675860074252</v>
       </c>
       <c r="E22" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F22" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>62.21243346110788</v>
+        <v>10.10952043743003</v>
       </c>
       <c r="D23" t="n">
-        <v>54.25956671035092</v>
+        <v>8.817179590432024</v>
       </c>
       <c r="E23" t="n">
-        <v>15.69553054952976</v>
+        <v>2.550523714298587</v>
       </c>
       <c r="F23" t="n">
-        <v>13.31203028272981</v>
+        <v>2.163204920943593</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
